--- a/sample_data/route_template.xlsx
+++ b/sample_data/route_template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +515,16 @@
       <c r="T1" t="inlineStr">
         <is>
           <t>Сколько раз посещаем в месяц</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Оценка</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Результат</t>
         </is>
       </c>
     </row>
@@ -539,6 +549,8 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
